--- a/ResourcesBD/Selling_Category_Bulk_Upload.xlsx
+++ b/ResourcesBD/Selling_Category_Bulk_Upload.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Excel Template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" concurrentManualCount="8"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Distributor Code*</t>
   </si>
@@ -178,6 +178,12 @@
   </si>
   <si>
     <t>845641778651</t>
+  </si>
+  <si>
+    <t>SEC000000033</t>
+  </si>
+  <si>
+    <t>SEC000000021</t>
   </si>
 </sst>
 </file>
@@ -496,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.6328125" bestFit="1" customWidth="1"/>
@@ -919,6 +925,22 @@
         <v>44</v>
       </c>
     </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="1">
+        <v>15437620</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="1">
+        <v>15437620</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
